--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512445_1ºCA1ºCBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512445_1ºCA1ºCBFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6971</v>
+        <v>7.13</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8165</v>
+        <v>8.305899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1194</v>
+        <v>-1.176</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5175</v>
+        <v>4.5633</v>
       </c>
       <c r="H2" t="n">
-        <v>5.693</v>
+        <v>5.7498</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1755</v>
+        <v>-1.1866</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8625</v>
+        <v>4.0263</v>
       </c>
       <c r="K2" t="n">
-        <v>5.0586</v>
+        <v>5.1932</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.196</v>
+        <v>-1.1669</v>
       </c>
       <c r="M2" t="n">
-        <v>0.655</v>
+        <v>0.537</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6344</v>
+        <v>0.5567</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4197</v>
+        <v>-0.0965</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0243</v>
+        <v>0.1412</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3954</v>
+        <v>-0.2377</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9994</v>
+        <v>3.0526</v>
       </c>
       <c r="W2" t="n">
-        <v>4.9786</v>
+        <v>5.1121</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9791</v>
+        <v>-2.0595</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3097</v>
+        <v>4.5742</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8898</v>
+        <v>3.217</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4199</v>
+        <v>1.3572</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6199</v>
+        <v>2.6466</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7613</v>
+        <v>1.8397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8585</v>
+        <v>0.8069</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3651</v>
+        <v>1.4939</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2051</v>
+        <v>1.3318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2548</v>
+        <v>1.1528</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5562</v>
+        <v>0.508</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6986</v>
+        <v>0.6448</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6895</v>
+        <v>0.9538</v>
       </c>
       <c r="T3" t="n">
-        <v>1.325</v>
+        <v>0.5021</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3646</v>
+        <v>0.4517</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9156</v>
+        <v>4.0769</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2898</v>
+        <v>2.5038</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6258</v>
+        <v>1.5731</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7757</v>
+        <v>3.7759</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2473</v>
+        <v>1.2048</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5284</v>
+        <v>2.571</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5853</v>
+        <v>2.6902</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2199</v>
+        <v>0.2258</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3654</v>
+        <v>2.4644</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1904</v>
+        <v>1.0857</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0274</v>
+        <v>0.979</v>
       </c>
       <c r="O4" t="n">
-        <v>0.163</v>
+        <v>0.1067</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4006</v>
+        <v>-0.1984</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1046</v>
+        <v>0.2031</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5052</v>
+        <v>-0.4015</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131</v>
+        <v>2.3786</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2655</v>
+        <v>1.4987</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8799</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3378</v>
+        <v>1.3461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9797</v>
+        <v>1.0058</v>
       </c>
       <c r="I5" t="n">
-        <v>0.358</v>
+        <v>0.3403</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9815</v>
+        <v>1.0381</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9016</v>
+        <v>0.9571</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3562</v>
+        <v>0.308</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0487</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4066</v>
+        <v>-0.1885</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5157</v>
+        <v>-0.371</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1091</v>
+        <v>0.1825</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6011</v>
+        <v>1.6201</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6408</v>
+        <v>2.9421</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0397</v>
+        <v>-1.322</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7846</v>
+        <v>2.7858</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4268</v>
+        <v>0.4192</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3578</v>
+        <v>2.3666</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8214</v>
+        <v>2.895</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3417</v>
+        <v>0.3823</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4796</v>
+        <v>2.5126</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0368</v>
+        <v>-0.1091</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0851</v>
+        <v>0.0369</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3235</v>
+        <v>-0.302</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3801</v>
+        <v>-0.2003</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0566</v>
+        <v>-0.1018</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1998</v>
+        <v>1.4547</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1998</v>
+        <v>1.2942</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.1605</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1998</v>
+        <v>2.4238</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.9166</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1998</v>
+        <v>0.5072</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1998</v>
+        <v>1.7842</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.6626</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1998</v>
+        <v>0.1216</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.3856</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.527</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2953</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2317</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9996</v>
+        <v>1.2158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9594</v>
+        <v>1.2158</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0403</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4382</v>
+        <v>1.2158</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8977</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5405</v>
+        <v>1.2158</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7395</v>
+        <v>1.2158</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6195</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>1.2158</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6986</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2781</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.039</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4588</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0002</v>
+        <v>1.0979</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5244</v>
+        <v>0.4251</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5242</v>
+        <v>0.6728</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4842</v>
+        <v>-0.0548</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.778</v>
+        <v>0.9453</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2622</v>
+        <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5072</v>
+        <v>-1.455</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3345</v>
+        <v>-0.2154</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8416</v>
+        <v>-1.2396</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.023</v>
+        <v>1.4002</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4435</v>
+        <v>1.1606</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4205</v>
+        <v>0.2396</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>-0.3895</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6002</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0843</v>
+        <v>-0.5678</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0313</v>
+        <v>-0.1726</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.053</v>
+        <v>-0.3953</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9416</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1399</v>
+        <v>0.6123</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6056</v>
+        <v>0.0617</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4657</v>
+        <v>0.5506</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1051</v>
+        <v>1.5071</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9085</v>
+        <v>-0.7671</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0136</v>
+        <v>2.2742</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6449</v>
+        <v>1.6399</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3327</v>
+        <v>-0.2488</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3122</v>
+        <v>1.8887</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5398</v>
+        <v>-0.1328</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2411</v>
+        <v>-0.5184</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2986</v>
+        <v>0.3856</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4001</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.775</v>
+        <v>-0.5053</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8148</v>
+        <v>0.0992</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3995</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3772</v>
+        <v>0.0266</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6173</v>
+        <v>-1.1346</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2401</v>
+        <v>1.1612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6067</v>
+        <v>0.6098</v>
       </c>
       <c r="H11" t="n">
-        <v>0.911</v>
+        <v>0.9226</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3043</v>
+        <v>-0.3129</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3654</v>
+        <v>0.4596</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9615</v>
+        <v>1.0187</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5961</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2413</v>
+        <v>0.1501</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0505</v>
+        <v>-0.096</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1039</v>
+        <v>-0.7</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9024</v>
+        <v>-0.5427</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2015</v>
+        <v>-0.1574</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4227</v>
+        <v>-0.3066</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0429</v>
+        <v>-0.9816</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6202</v>
+        <v>0.675</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5068</v>
+        <v>-0.5013</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1712</v>
+        <v>0.1632</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6562</v>
+        <v>-0.6106</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6998</v>
+        <v>0.7184</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.356</v>
+        <v>-1.329</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1494</v>
+        <v>0.1093</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5286</v>
+        <v>-0.5553</v>
       </c>
       <c r="O12" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5161</v>
+        <v>-0.3895</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3867</v>
+        <v>-0.371</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1294</v>
+        <v>-0.0185</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5868</v>
+        <v>-1.1759</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3293</v>
+        <v>-0.0624</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2574</v>
+        <v>-1.1135</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7285</v>
+        <v>-0.7595</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6485</v>
+        <v>-0.6784</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1219</v>
+        <v>0.1471</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0419</v>
+        <v>0.065</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8504</v>
+        <v>-0.9065</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7285</v>
+        <v>-0.7605</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8582</v>
+        <v>-0.4165</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4512</v>
+        <v>-0.2095</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.407</v>
+        <v>-0.207</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.6999</v>
+        <v>-2.0975</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6624</v>
+        <v>-1.2434</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0375</v>
+        <v>-0.854</v>
       </c>
       <c r="G14" t="n">
-        <v>0.353</v>
+        <v>0.376</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8605</v>
+        <v>-0.8266</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2135</v>
+        <v>1.2027</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3088</v>
+        <v>-0.1544</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6305</v>
+        <v>-1.5162</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3217</v>
+        <v>1.3618</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.5304</v>
       </c>
       <c r="N14" t="n">
-        <v>0.77</v>
+        <v>0.6896</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7467</v>
+        <v>0.3581</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1533</v>
+        <v>0.0794</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9</v>
+        <v>0.2787</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.6272</v>
+        <v>20.6071</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2797</v>
+        <v>18.0423</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3476</v>
+        <v>2.564799999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>19.777</v>
+        <v>19.9346</v>
       </c>
       <c r="H15" t="n">
-        <v>11.7095</v>
+        <v>11.8949</v>
       </c>
       <c r="I15" t="n">
-        <v>8.067300000000001</v>
+        <v>8.0396</v>
       </c>
       <c r="J15" t="n">
-        <v>13.9397</v>
+        <v>15.1701</v>
       </c>
       <c r="K15" t="n">
-        <v>8.790000000000003</v>
+        <v>9.591600000000003</v>
       </c>
       <c r="L15" t="n">
-        <v>5.1497</v>
+        <v>5.5786</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8371</v>
+        <v>4.7647</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9194</v>
+        <v>2.3033</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9177</v>
+        <v>2.4613</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0008</v>
+        <v>2.920800000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.0017</v>
+        <v>-5.8422</v>
       </c>
       <c r="R15" t="n">
-        <v>9.0025</v>
+        <v>8.7631</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.4907</v>
+        <v>-2.5796</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.9557</v>
+        <v>-1.8411</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.7388000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3400999999999996</v>
+        <v>0.331</v>
       </c>
       <c r="W15" t="n">
-        <v>10.2973</v>
+        <v>10.5554</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.9572</v>
+        <v>-10.2243</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5369</v>
+        <v>1.5119</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6322</v>
+        <v>2.3514</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0953</v>
+        <v>-0.8395</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5109</v>
+        <v>-0.5295</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.78</v>
+        <v>-2.7972</v>
       </c>
       <c r="I16" t="n">
-        <v>2.269</v>
+        <v>2.2677</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5256</v>
+        <v>0.6007</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.994</v>
+        <v>-1.9525</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5196</v>
+        <v>2.5532</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0366</v>
+        <v>-1.1302</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7859</v>
+        <v>-0.8447</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1881</v>
+        <v>0.1514</v>
       </c>
       <c r="T16" t="n">
-        <v>0.647</v>
+        <v>0.2501</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4588</v>
+        <v>-0.0988</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2393</v>
+        <v>0.9399</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2901</v>
+        <v>1.6218</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0508</v>
+        <v>-0.6819</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3438</v>
+        <v>-1.9222</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8064</v>
+        <v>-2.7279</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5374</v>
+        <v>0.8058</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2363</v>
+        <v>-0.2973</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3563</v>
+        <v>-1.5214</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>1.2241</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1075</v>
+        <v>-1.6249</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4501</v>
+        <v>-1.2065</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6574</v>
+        <v>-0.4184</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9235</v>
+        <v>-0.0279</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0671</v>
+        <v>-0.192</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8564</v>
+        <v>0.164</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2598</v>
+        <v>2.1111</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4596</v>
+        <v>2.1111</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0048</v>
+        <v>0.7276</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6388</v>
+        <v>0.3477</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.3799</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0319</v>
+        <v>-0.9782</v>
       </c>
       <c r="H18" t="n">
-        <v>0.526</v>
+        <v>0.5779</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5579</v>
+        <v>-1.5561</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3908</v>
+        <v>0.5809</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7049</v>
+        <v>1.8449</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3141</v>
+        <v>-1.264</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4227</v>
+        <v>-1.5591</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1789</v>
+        <v>-1.2671</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0969</v>
+        <v>0.7379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.889</v>
+        <v>-0.1495</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9859</v>
+        <v>0.8874</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5399</v>
+        <v>1.5521</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3479</v>
+        <v>-0.699</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6177</v>
+        <v>0.3976</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9656</v>
+        <v>-1.0966</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9044</v>
+        <v>-1.1678</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6818</v>
+        <v>-0.5486</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7774</v>
+        <v>-0.6192</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4105</v>
+        <v>1.0807</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5741</v>
+        <v>0.4644</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1636</v>
+        <v>0.6163</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4939</v>
+        <v>-2.2485</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1077</v>
+        <v>-1.0131</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3862</v>
+        <v>-1.2355</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8002</v>
+        <v>0.9737</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3032</v>
+        <v>0.4689</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0313</v>
+        <v>0.0111</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2719</v>
+        <v>0.4578</v>
       </c>
       <c r="V19" t="n">
-        <v>2.0594</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0594</v>
+        <v>0.2795</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7575</v>
+        <v>-1.3213</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3252</v>
+        <v>0.6143</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0827</v>
+        <v>-1.9356</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0946</v>
+        <v>-2.3982</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4791</v>
+        <v>-1.8356</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6155</v>
+        <v>-0.5626</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9854000000000001</v>
+        <v>-0.1811</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4217</v>
+        <v>-0.3027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5637</v>
+        <v>0.1216</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0801</v>
+        <v>-2.217</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9008</v>
+        <v>-1.5329</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1793</v>
+        <v>-0.6842</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3371</v>
+        <v>1.3816</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.2686</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2569</v>
+        <v>1.113</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2598</v>
+        <v>1.5005</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2598</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2568</v>
+        <v>-1.398</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8117</v>
+        <v>-1.7621</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.3641</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6754</v>
+        <v>-0.6871</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0822</v>
+        <v>-1.0858</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.618</v>
+        <v>-0.6029</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.618</v>
+        <v>-0.6029</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.419</v>
+        <v>0.2628</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1934</v>
+        <v>-0.1855</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6123</v>
+        <v>0.4483</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>V. VINOS ALTEMIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2925</v>
+        <v>-1.4077</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5193</v>
+        <v>-0.8854</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8118</v>
+        <v>-0.5224</v>
       </c>
       <c r="G22" t="n">
-        <v>1.314</v>
+        <v>0.0985</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4847</v>
+        <v>-0.5142</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1706</v>
+        <v>0.6127</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6795</v>
+        <v>1.0352</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5995</v>
+        <v>0.4029</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08</v>
+        <v>0.6323</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3655</v>
+        <v>-0.9367</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1149</v>
+        <v>-0.9171</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2506</v>
+        <v>-0.0197</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.4004</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1934</v>
+        <v>0.4412</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8403</v>
+        <v>0.0268</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3531</v>
+        <v>0.4144</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3995</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. VINOS ALTEMIR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6657</v>
+        <v>-2.107</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9258</v>
+        <v>0.1118</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.74</v>
+        <v>-2.2188</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1338</v>
+        <v>1.2693</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4886</v>
+        <v>1.4737</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6224</v>
+        <v>-0.2044</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9635</v>
+        <v>1.7232</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3617</v>
+        <v>1.6421</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6018</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8297</v>
+        <v>-0.4539</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.1684</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0206</v>
+        <v>-0.2855</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0006</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.201</v>
+        <v>0.4289</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1113</v>
+        <v>0.336</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0898</v>
+        <v>0.093</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.4421</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9166</v>
+        <v>-2.4928</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0309</v>
+        <v>-0.2287</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9474</v>
+        <v>-2.2642</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9129</v>
+        <v>-0.946</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.153</v>
+        <v>-0.176</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7599</v>
+        <v>-0.77</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.598</v>
+        <v>-0.5829</v>
       </c>
       <c r="K24" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3149</v>
+        <v>-0.3631</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9361</v>
+        <v>0.4211</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3691</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.3463</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1398</v>
+        <v>-2.1626</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6852</v>
+        <v>-2.8806</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8021</v>
+        <v>-1.0462</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8831</v>
+        <v>-1.8344</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.0059</v>
+        <v>-5.9226</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.6989</v>
+        <v>-2.6257</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.307</v>
+        <v>-3.2969</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.9189</v>
+        <v>-3.6859</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.9268</v>
+        <v>-1.7573</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9921</v>
+        <v>-1.9286</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.087</v>
+        <v>-2.2367</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7721</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.3149</v>
+        <v>-1.3684</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.619</v>
+        <v>0.0741</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4822</v>
+        <v>-0.0498</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1368</v>
+        <v>0.1239</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7396</v>
+        <v>2.7732</v>
       </c>
       <c r="W25" t="n">
-        <v>3.5993</v>
+        <v>3.6632</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1244</v>
+        <v>-3.4337</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.655</v>
+        <v>-2.0199</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4694</v>
+        <v>-1.4138</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.7962</v>
+        <v>-2.7604</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8041</v>
+        <v>-0.8318</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.9921</v>
+        <v>-1.9286</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.0883</v>
+        <v>-1.9802</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.618</v>
+        <v>-0.6029</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.4703</v>
+        <v>-1.3773</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7079</v>
+        <v>-0.7802</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1861</v>
+        <v>-0.2289</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5285</v>
+        <v>0.1583</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5667</v>
+        <v>-0.0397</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0382</v>
+        <v>0.198</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3615</v>
+        <v>-5.5266</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.9295</v>
+        <v>-2.0672</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.4319</v>
+        <v>-3.4594</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.9486</v>
+        <v>-3.9903</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.746</v>
+        <v>-0.8036</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.2026</v>
+        <v>-3.1867</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.512</v>
+        <v>-2.4549</v>
       </c>
       <c r="K27" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.552</v>
+        <v>-2.4959</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.4365</v>
+        <v>-1.5354</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.7859</v>
+        <v>-0.8447</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P27" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6463</v>
+        <v>0.6011</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5825</v>
+        <v>0.3876</v>
       </c>
       <c r="U27" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.2134</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="28">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-18.6271</v>
+        <v>-18.0873</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.3475</v>
+        <v>-2.564900000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-14.2795</v>
+        <v>-15.5226</v>
       </c>
       <c r="G28" t="n">
-        <v>-19.7768</v>
+        <v>-19.9345</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.7094</v>
+        <v>-11.8948</v>
       </c>
       <c r="I28" t="n">
-        <v>-8.067399999999999</v>
+        <v>-8.0396</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.837199999999999</v>
+        <v>-4.7645</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.9194</v>
+        <v>-2.3032</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.9178</v>
+        <v>-2.4612</v>
       </c>
       <c r="M28" t="n">
-        <v>-13.9397</v>
+        <v>-15.1699</v>
       </c>
       <c r="N28" t="n">
-        <v>-8.789899999999999</v>
+        <v>-9.591799999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>-5.149699999999999</v>
+        <v>-5.5785</v>
       </c>
       <c r="P28" t="n">
-        <v>-3.0009</v>
+        <v>-2.9212</v>
       </c>
       <c r="Q28" t="n">
-        <v>-9.002699999999999</v>
+        <v>-8.763300000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>6.0017</v>
+        <v>5.8421</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4907</v>
+        <v>5.099399999999998</v>
       </c>
       <c r="T28" t="n">
-        <v>0.5348999999999999</v>
+        <v>0.7384999999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>3.9558</v>
+        <v>4.3607</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.3400999999999996</v>
+        <v>-0.3309999999999991</v>
       </c>
       <c r="W28" t="n">
-        <v>9.9572</v>
+        <v>10.2243</v>
       </c>
       <c r="X28" t="n">
-        <v>-10.2972</v>
+        <v>-10.5554</v>
       </c>
     </row>
   </sheetData>
